--- a/sites/betzel-hateena/SEO-QA-betzel-hateena.xlsx
+++ b/sites/betzel-hateena/SEO-QA-betzel-hateena.xlsx
@@ -962,7 +962,7 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>54 images</t>
+          <t>52 images</t>
         </is>
       </c>
       <c r="F12" s="16" t="n"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>17 internal links, all &lt; 400</t>
+          <t>16 internal links, all &lt; 400</t>
         </is>
       </c>
       <c r="F24" s="20" t="n"/>

--- a/sites/betzel-hateena/SEO-QA-betzel-hateena.xlsx
+++ b/sites/betzel-hateena/SEO-QA-betzel-hateena.xlsx
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>site shows 052-4848123, nimrod@gesher-lab.co.il, קלע אלון 90; compare with the spec</t>
+          <t>site shows 052-4848123, nimrod@gesher-lab.co.il, קלע אלון 90, רמת הגולן; compare with the spec</t>
         </is>
       </c>
       <c r="F36" s="20" t="n"/>
